--- a/사용자템플릿_엑셀_제작도.xlsx
+++ b/사용자템플릿_엑셀_제작도.xlsx
@@ -513,11 +513,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>{Image_2}</t>
+    <t>{View_6}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>{Image_3}</t>
+    <t>{View_5}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>

--- a/사용자템플릿_엑셀_제작도.xlsx
+++ b/사용자템플릿_엑셀_제작도.xlsx
@@ -521,7 +521,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>{Image_4}</t>
+    <t>{View_7}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
